--- a/名前カード・座席表メーカー.xlsx
+++ b/名前カード・座席表メーカー.xlsx
@@ -20,10 +20,12 @@
     <sheet name="縦書き (小)" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="縦書き (小・ふりがななし)" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="座席表" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="座席表 （低学年用）" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="提出物チェック表" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="班分け表" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="使い方" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="座席表 (黒板が下)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="座席表 （低学年用）" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="座席表 （低学年用・黒板が下）" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="提出物チェック表" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="班分け表" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="使い方" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'名簿'!$B$1:$D$37</definedName>
@@ -33,8 +35,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">OFFSET('縦書き (大・ふりがななし)'!$A$1,0,0,CEILING(IFERROR(LOOKUP(2,1/(名簿!$C$3:$C$37&amp;名簿!$D$3:$D$37&lt;&gt;""),ROW(名簿!$C$3:$C$37)-2),1)/10,1)*2,10)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">OFFSET('縦書き (中)'!$A$1,0,0,CEILING(IFERROR(LOOKUP(2,1/(名簿!$C$3:$C$37&amp;名簿!$D$3:$D$37&lt;&gt;""),ROW(名簿!$C$3:$C$37)-2),1)/20,1)*2,20)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">OFFSET('縦書き (中・ふりがななし)'!$A$1,0,0,CEILING(IFERROR(LOOKUP(2,1/(名簿!$C$3:$C$37&amp;名簿!$D$3:$D$37&lt;&gt;""),ROW(名簿!$C$3:$C$37)-2),1)/20,1)*2,10)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'提出物チェック表'!$A$1:$R$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'班分け表'!$F$1:$P$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'提出物チェック表'!$A$1:$R$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'班分け表'!$F$1:$P$21</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -4508,7 +4510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.125" customWidth="1" style="35" min="1" max="2"/>
@@ -5336,7 +5338,654 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.125" customWidth="1" style="4" min="1" max="1"/>
+    <col width="2" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11.125" customWidth="1" style="4" min="4" max="4"/>
+    <col width="2" customWidth="1" style="4" min="6" max="6"/>
+    <col width="11.125" customWidth="1" style="4" min="7" max="7"/>
+    <col width="2" customWidth="1" style="4" min="9" max="9"/>
+    <col width="11.125" customWidth="1" style="4" min="10" max="10"/>
+    <col width="2" customWidth="1" style="4" min="12" max="12"/>
+    <col width="11" customWidth="1" style="4" min="13" max="13"/>
+    <col width="2" customWidth="1" style="4" min="15" max="15"/>
+    <col width="11" customWidth="1" style="4" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1" s="4">
+      <c r="A1" s="2">
+        <f>IF('座席表'!Y9="","",IFERROR(VLOOKUP('座席表'!Y9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B1" s="73" t="n"/>
+      <c r="D1" s="2">
+        <f>IF('座席表'!X9="","",IFERROR(VLOOKUP('座席表'!X9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E1" s="73" t="n"/>
+      <c r="G1" s="2">
+        <f>IF('座席表'!W9="","",IFERROR(VLOOKUP('座席表'!W9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H1" s="73" t="n"/>
+      <c r="J1" s="2">
+        <f>IF('座席表'!V9="","",IFERROR(VLOOKUP('座席表'!V9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K1" s="73" t="n"/>
+      <c r="M1" s="2">
+        <f>IF('座席表'!U9="","",IFERROR(VLOOKUP('座席表'!U9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N1" s="73" t="n"/>
+      <c r="P1" s="2">
+        <f>IF('座席表'!T9="","",IFERROR(VLOOKUP('座席表'!T9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q1" s="73" t="n"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" s="4">
+      <c r="A2" s="1">
+        <f>IF('座席表'!Y9="","",IFERROR(VLOOKUP('座席表'!Y9,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B2" s="69" t="n"/>
+      <c r="D2" s="1">
+        <f>IF('座席表'!X9="","",IFERROR(VLOOKUP('座席表'!X9,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="42" t="n"/>
+      <c r="G2" s="1">
+        <f>IF('座席表'!W9="","",IFERROR(VLOOKUP('座席表'!W9,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="42" t="n"/>
+      <c r="J2" s="1">
+        <f>IF('座席表'!V9="","",IFERROR(VLOOKUP('座席表'!V9,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K2" s="69" t="n"/>
+      <c r="L2" s="42" t="n"/>
+      <c r="M2" s="1">
+        <f>IF('座席表'!U9="","",IFERROR(VLOOKUP('座席表'!U9,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N2" s="69" t="n"/>
+      <c r="O2" s="42" t="n"/>
+      <c r="P2" s="1">
+        <f>IF('座席表'!T9="","",IFERROR(VLOOKUP('座席表'!T9,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q2" s="69" t="n"/>
+      <c r="R2" s="42" t="n"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" s="4">
+      <c r="A3" s="70" t="n"/>
+      <c r="B3" s="72" t="n"/>
+      <c r="D3" s="70" t="n"/>
+      <c r="E3" s="72" t="n"/>
+      <c r="F3" s="42" t="n"/>
+      <c r="G3" s="70" t="n"/>
+      <c r="H3" s="72" t="n"/>
+      <c r="I3" s="42" t="n"/>
+      <c r="J3" s="70" t="n"/>
+      <c r="K3" s="72" t="n"/>
+      <c r="L3" s="42" t="n"/>
+      <c r="M3" s="70" t="n"/>
+      <c r="N3" s="72" t="n"/>
+      <c r="O3" s="42" t="n"/>
+      <c r="P3" s="70" t="n"/>
+      <c r="Q3" s="72" t="n"/>
+      <c r="R3" s="42" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" s="4"/>
+    <row r="5" ht="22.5" customHeight="1" s="4">
+      <c r="A5" s="2">
+        <f>IF('座席表'!Y8="","",IFERROR(VLOOKUP('座席表'!Y8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B5" s="73" t="n"/>
+      <c r="D5" s="2">
+        <f>IF('座席表'!X8="","",IFERROR(VLOOKUP('座席表'!X8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E5" s="73" t="n"/>
+      <c r="G5" s="2">
+        <f>IF('座席表'!W8="","",IFERROR(VLOOKUP('座席表'!W8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H5" s="73" t="n"/>
+      <c r="J5" s="2">
+        <f>IF('座席表'!V8="","",IFERROR(VLOOKUP('座席表'!V8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K5" s="73" t="n"/>
+      <c r="M5" s="2">
+        <f>IF('座席表'!U8="","",IFERROR(VLOOKUP('座席表'!U8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N5" s="73" t="n"/>
+      <c r="P5" s="2">
+        <f>IF('座席表'!T8="","",IFERROR(VLOOKUP('座席表'!T8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="73" t="n"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" s="4">
+      <c r="A6" s="1">
+        <f>IF('座席表'!Y8="","",IFERROR(VLOOKUP('座席表'!Y8,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B6" s="69" t="n"/>
+      <c r="D6" s="1">
+        <f>IF('座席表'!X8="","",IFERROR(VLOOKUP('座席表'!X8,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E6" s="69" t="n"/>
+      <c r="F6" s="42" t="n"/>
+      <c r="G6" s="1">
+        <f>IF('座席表'!W8="","",IFERROR(VLOOKUP('座席表'!W8,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H6" s="69" t="n"/>
+      <c r="I6" s="42" t="n"/>
+      <c r="J6" s="1">
+        <f>IF('座席表'!V8="","",IFERROR(VLOOKUP('座席表'!V8,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K6" s="69" t="n"/>
+      <c r="L6" s="42" t="n"/>
+      <c r="M6" s="1">
+        <f>IF('座席表'!U8="","",IFERROR(VLOOKUP('座席表'!U8,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N6" s="69" t="n"/>
+      <c r="O6" s="42" t="n"/>
+      <c r="P6" s="1">
+        <f>IF('座席表'!T8="","",IFERROR(VLOOKUP('座席表'!T8,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="69" t="n"/>
+      <c r="R6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1" s="4">
+      <c r="A7" s="70" t="n"/>
+      <c r="B7" s="72" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="72" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="72" t="n"/>
+      <c r="I7" s="42" t="n"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="72" t="n"/>
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="70" t="n"/>
+      <c r="N7" s="72" t="n"/>
+      <c r="O7" s="42" t="n"/>
+      <c r="P7" s="70" t="n"/>
+      <c r="Q7" s="72" t="n"/>
+      <c r="R7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="22.5" customHeight="1" s="4"/>
+    <row r="9" ht="22.5" customHeight="1" s="4">
+      <c r="A9" s="2">
+        <f>IF('座席表'!Y7="","",IFERROR(VLOOKUP('座席表'!Y7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B9" s="73" t="n"/>
+      <c r="D9" s="2">
+        <f>IF('座席表'!X7="","",IFERROR(VLOOKUP('座席表'!X7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="73" t="n"/>
+      <c r="G9" s="2">
+        <f>IF('座席表'!W7="","",IFERROR(VLOOKUP('座席表'!W7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H9" s="73" t="n"/>
+      <c r="J9" s="2">
+        <f>IF('座席表'!V7="","",IFERROR(VLOOKUP('座席表'!V7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K9" s="73" t="n"/>
+      <c r="M9" s="2">
+        <f>IF('座席表'!U7="","",IFERROR(VLOOKUP('座席表'!U7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N9" s="73" t="n"/>
+      <c r="P9" s="2">
+        <f>IF('座席表'!T7="","",IFERROR(VLOOKUP('座席表'!T7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="73" t="n"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" s="4">
+      <c r="A10" s="1">
+        <f>IF('座席表'!Y7="","",IFERROR(VLOOKUP('座席表'!Y7,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B10" s="69" t="n"/>
+      <c r="D10" s="1">
+        <f>IF('座席表'!X7="","",IFERROR(VLOOKUP('座席表'!X7,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="69" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="1">
+        <f>IF('座席表'!W7="","",IFERROR(VLOOKUP('座席表'!W7,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H10" s="69" t="n"/>
+      <c r="I10" s="42" t="n"/>
+      <c r="J10" s="1">
+        <f>IF('座席表'!V7="","",IFERROR(VLOOKUP('座席表'!V7,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K10" s="69" t="n"/>
+      <c r="L10" s="42" t="n"/>
+      <c r="M10" s="1">
+        <f>IF('座席表'!U7="","",IFERROR(VLOOKUP('座席表'!U7,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N10" s="69" t="n"/>
+      <c r="O10" s="42" t="n"/>
+      <c r="P10" s="1">
+        <f>IF('座席表'!T7="","",IFERROR(VLOOKUP('座席表'!T7,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="69" t="n"/>
+      <c r="R10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" s="4">
+      <c r="A11" s="70" t="n"/>
+      <c r="B11" s="72" t="n"/>
+      <c r="D11" s="70" t="n"/>
+      <c r="E11" s="72" t="n"/>
+      <c r="F11" s="42" t="n"/>
+      <c r="G11" s="70" t="n"/>
+      <c r="H11" s="72" t="n"/>
+      <c r="I11" s="42" t="n"/>
+      <c r="J11" s="70" t="n"/>
+      <c r="K11" s="72" t="n"/>
+      <c r="L11" s="42" t="n"/>
+      <c r="M11" s="70" t="n"/>
+      <c r="N11" s="72" t="n"/>
+      <c r="O11" s="42" t="n"/>
+      <c r="P11" s="70" t="n"/>
+      <c r="Q11" s="72" t="n"/>
+      <c r="R11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" s="4"/>
+    <row r="13" ht="22.5" customHeight="1" s="4">
+      <c r="A13" s="2">
+        <f>IF('座席表'!Y6="","",IFERROR(VLOOKUP('座席表'!Y6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B13" s="73" t="n"/>
+      <c r="D13" s="2">
+        <f>IF('座席表'!X6="","",IFERROR(VLOOKUP('座席表'!X6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="73" t="n"/>
+      <c r="G13" s="2">
+        <f>IF('座席表'!W6="","",IFERROR(VLOOKUP('座席表'!W6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H13" s="73" t="n"/>
+      <c r="J13" s="2">
+        <f>IF('座席表'!V6="","",IFERROR(VLOOKUP('座席表'!V6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K13" s="73" t="n"/>
+      <c r="M13" s="2">
+        <f>IF('座席表'!U6="","",IFERROR(VLOOKUP('座席表'!U6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N13" s="73" t="n"/>
+      <c r="P13" s="2">
+        <f>IF('座席表'!T6="","",IFERROR(VLOOKUP('座席表'!T6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="73" t="n"/>
+    </row>
+    <row r="14" ht="22.5" customHeight="1" s="4">
+      <c r="A14" s="1">
+        <f>IF('座席表'!Y6="","",IFERROR(VLOOKUP('座席表'!Y6,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B14" s="69" t="n"/>
+      <c r="D14" s="1">
+        <f>IF('座席表'!X6="","",IFERROR(VLOOKUP('座席表'!X6,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E14" s="69" t="n"/>
+      <c r="F14" s="42" t="n"/>
+      <c r="G14" s="1">
+        <f>IF('座席表'!W6="","",IFERROR(VLOOKUP('座席表'!W6,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H14" s="69" t="n"/>
+      <c r="I14" s="42" t="n"/>
+      <c r="J14" s="1">
+        <f>IF('座席表'!V6="","",IFERROR(VLOOKUP('座席表'!V6,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K14" s="69" t="n"/>
+      <c r="L14" s="42" t="n"/>
+      <c r="M14" s="1">
+        <f>IF('座席表'!U6="","",IFERROR(VLOOKUP('座席表'!U6,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N14" s="69" t="n"/>
+      <c r="O14" s="42" t="n"/>
+      <c r="P14" s="1">
+        <f>IF('座席表'!T6="","",IFERROR(VLOOKUP('座席表'!T6,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="69" t="n"/>
+      <c r="R14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="22.5" customHeight="1" s="4">
+      <c r="A15" s="70" t="n"/>
+      <c r="B15" s="72" t="n"/>
+      <c r="D15" s="70" t="n"/>
+      <c r="E15" s="72" t="n"/>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="70" t="n"/>
+      <c r="H15" s="72" t="n"/>
+      <c r="I15" s="42" t="n"/>
+      <c r="J15" s="70" t="n"/>
+      <c r="K15" s="72" t="n"/>
+      <c r="L15" s="42" t="n"/>
+      <c r="M15" s="70" t="n"/>
+      <c r="N15" s="72" t="n"/>
+      <c r="O15" s="42" t="n"/>
+      <c r="P15" s="70" t="n"/>
+      <c r="Q15" s="72" t="n"/>
+      <c r="R15" s="42" t="n"/>
+    </row>
+    <row r="16" ht="22.5" customHeight="1" s="4"/>
+    <row r="17" ht="22.5" customHeight="1" s="4">
+      <c r="A17" s="2">
+        <f>IF('座席表'!Y5="","",IFERROR(VLOOKUP('座席表'!Y5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B17" s="73" t="n"/>
+      <c r="D17" s="2">
+        <f>IF('座席表'!X5="","",IFERROR(VLOOKUP('座席表'!X5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="73" t="n"/>
+      <c r="G17" s="2">
+        <f>IF('座席表'!W5="","",IFERROR(VLOOKUP('座席表'!W5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H17" s="73" t="n"/>
+      <c r="J17" s="2">
+        <f>IF('座席表'!V5="","",IFERROR(VLOOKUP('座席表'!V5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K17" s="73" t="n"/>
+      <c r="M17" s="2">
+        <f>IF('座席表'!U5="","",IFERROR(VLOOKUP('座席表'!U5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N17" s="73" t="n"/>
+      <c r="P17" s="2">
+        <f>IF('座席表'!T5="","",IFERROR(VLOOKUP('座席表'!T5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="73" t="n"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1" s="4">
+      <c r="A18" s="1">
+        <f>IF('座席表'!Y5="","",IFERROR(VLOOKUP('座席表'!Y5,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B18" s="69" t="n"/>
+      <c r="D18" s="1">
+        <f>IF('座席表'!X5="","",IFERROR(VLOOKUP('座席表'!X5,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E18" s="69" t="n"/>
+      <c r="F18" s="42" t="n"/>
+      <c r="G18" s="1">
+        <f>IF('座席表'!W5="","",IFERROR(VLOOKUP('座席表'!W5,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H18" s="69" t="n"/>
+      <c r="I18" s="42" t="n"/>
+      <c r="J18" s="1">
+        <f>IF('座席表'!V5="","",IFERROR(VLOOKUP('座席表'!V5,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K18" s="69" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="1">
+        <f>IF('座席表'!U5="","",IFERROR(VLOOKUP('座席表'!U5,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N18" s="69" t="n"/>
+      <c r="O18" s="42" t="n"/>
+      <c r="P18" s="1">
+        <f>IF('座席表'!T5="","",IFERROR(VLOOKUP('座席表'!T5,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="69" t="n"/>
+      <c r="R18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="22.5" customHeight="1" s="4">
+      <c r="A19" s="70" t="n"/>
+      <c r="B19" s="72" t="n"/>
+      <c r="D19" s="70" t="n"/>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="70" t="n"/>
+      <c r="H19" s="72" t="n"/>
+      <c r="I19" s="42" t="n"/>
+      <c r="J19" s="70" t="n"/>
+      <c r="K19" s="72" t="n"/>
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="70" t="n"/>
+      <c r="N19" s="72" t="n"/>
+      <c r="O19" s="42" t="n"/>
+      <c r="P19" s="70" t="n"/>
+      <c r="Q19" s="72" t="n"/>
+      <c r="R19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" s="4"/>
+    <row r="21" ht="22.5" customHeight="1" s="4">
+      <c r="A21" s="2">
+        <f>IF('座席表'!Y4="","",IFERROR(VLOOKUP('座席表'!Y4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B21" s="73" t="n"/>
+      <c r="D21" s="2">
+        <f>IF('座席表'!X4="","",IFERROR(VLOOKUP('座席表'!X4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="73" t="n"/>
+      <c r="G21" s="2">
+        <f>IF('座席表'!W4="","",IFERROR(VLOOKUP('座席表'!W4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H21" s="73" t="n"/>
+      <c r="J21" s="2">
+        <f>IF('座席表'!V4="","",IFERROR(VLOOKUP('座席表'!V4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K21" s="73" t="n"/>
+      <c r="M21" s="2">
+        <f>IF('座席表'!U4="","",IFERROR(VLOOKUP('座席表'!U4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N21" s="73" t="n"/>
+      <c r="P21" s="2">
+        <f>IF('座席表'!T4="","",IFERROR(VLOOKUP('座席表'!T4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="73" t="n"/>
+    </row>
+    <row r="22" ht="22.5" customHeight="1" s="4">
+      <c r="A22" s="1">
+        <f>IF('座席表'!Y4="","",IFERROR(VLOOKUP('座席表'!Y4,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B22" s="69" t="n"/>
+      <c r="D22" s="1">
+        <f>IF('座席表'!X4="","",IFERROR(VLOOKUP('座席表'!X4,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="69" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="1">
+        <f>IF('座席表'!W4="","",IFERROR(VLOOKUP('座席表'!W4,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H22" s="69" t="n"/>
+      <c r="J22" s="1">
+        <f>IF('座席表'!V4="","",IFERROR(VLOOKUP('座席表'!V4,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K22" s="69" t="n"/>
+      <c r="M22" s="1">
+        <f>IF('座席表'!U4="","",IFERROR(VLOOKUP('座席表'!U4,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N22" s="69" t="n"/>
+      <c r="P22" s="1">
+        <f>IF('座席表'!T4="","",IFERROR(VLOOKUP('座席表'!T4,名簿!$B$3:$D$37,2,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="69" t="n"/>
+    </row>
+    <row r="23" ht="22.5" customHeight="1" s="4">
+      <c r="A23" s="70" t="n"/>
+      <c r="B23" s="72" t="n"/>
+      <c r="D23" s="70" t="n"/>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="70" t="n"/>
+      <c r="H23" s="72" t="n"/>
+      <c r="J23" s="70" t="n"/>
+      <c r="K23" s="72" t="n"/>
+      <c r="M23" s="70" t="n"/>
+      <c r="N23" s="72" t="n"/>
+      <c r="P23" s="70" t="n"/>
+      <c r="Q23" s="72" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1" s="4"/>
+    <row r="25" ht="13.5" customHeight="1" s="4">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>黒板</t>
+        </is>
+      </c>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="68" t="n"/>
+      <c r="J25" s="68" t="n"/>
+      <c r="K25" s="69" t="n"/>
+    </row>
+    <row r="26" ht="22.5" customHeight="1" s="4">
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="71" t="n"/>
+      <c r="I26" s="71" t="n"/>
+      <c r="J26" s="71" t="n"/>
+      <c r="K26" s="72" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="73">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G6:H7"/>
+    <mergeCell ref="M6:N7"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="D18:E19"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="J18:K19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M14:N15"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="J2:K3"/>
+    <mergeCell ref="G25:K26"/>
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="P18:Q19"/>
+    <mergeCell ref="D14:E15"/>
+    <mergeCell ref="D10:E11"/>
+    <mergeCell ref="P14:Q15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G22:H23"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="J14:K15"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="G2:H3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J10:K11"/>
+    <mergeCell ref="D6:E7"/>
+    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="P22:Q23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M2:N3"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J6:K7"/>
+    <mergeCell ref="P6:Q7"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G10:H11"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="M10:N11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="P2:Q3"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M22:N23"/>
+  </mergeCells>
+  <pageMargins left="0.197916666666667" right="0.125" top="0.291666666666667" bottom="0.21875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.125" customWidth="1" style="35" min="1" max="2"/>
@@ -6124,7 +6773,620 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.125" customWidth="1" style="4" min="1" max="1"/>
+    <col width="2" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11.125" customWidth="1" style="4" min="4" max="4"/>
+    <col width="2" customWidth="1" style="4" min="6" max="6"/>
+    <col width="11.125" customWidth="1" style="4" min="7" max="7"/>
+    <col width="2" customWidth="1" style="4" min="9" max="9"/>
+    <col width="11.125" customWidth="1" style="4" min="10" max="10"/>
+    <col width="2" customWidth="1" style="4" min="12" max="12"/>
+    <col width="11" customWidth="1" style="4" min="13" max="13"/>
+    <col width="2" customWidth="1" style="4" min="15" max="15"/>
+    <col width="11" customWidth="1" style="4" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1" s="4">
+      <c r="A1" s="1">
+        <f>IF('座席表 （低学年用）'!Y9="","",IFERROR(VLOOKUP('座席表 （低学年用）'!Y9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B1" s="69" t="n"/>
+      <c r="D1" s="1">
+        <f>IF('座席表 （低学年用）'!X9="","",IFERROR(VLOOKUP('座席表 （低学年用）'!X9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="46" t="n"/>
+      <c r="G1" s="1">
+        <f>IF('座席表 （低学年用）'!W9="","",IFERROR(VLOOKUP('座席表 （低学年用）'!W9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="46" t="n"/>
+      <c r="J1" s="1">
+        <f>IF('座席表 （低学年用）'!V9="","",IFERROR(VLOOKUP('座席表 （低学年用）'!V9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="46" t="n"/>
+      <c r="M1" s="1">
+        <f>IF('座席表 （低学年用）'!U9="","",IFERROR(VLOOKUP('座席表 （低学年用）'!U9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="46" t="n"/>
+      <c r="P1" s="1">
+        <f>IF('座席表 （低学年用）'!T9="","",IFERROR(VLOOKUP('座席表 （低学年用）'!T9,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="46" t="n"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" s="4">
+      <c r="A2" s="74" t="n"/>
+      <c r="B2" s="75" t="n"/>
+      <c r="D2" s="74" t="n"/>
+      <c r="E2" s="75" t="n"/>
+      <c r="F2" s="46" t="n"/>
+      <c r="G2" s="74" t="n"/>
+      <c r="H2" s="75" t="n"/>
+      <c r="I2" s="46" t="n"/>
+      <c r="J2" s="74" t="n"/>
+      <c r="K2" s="75" t="n"/>
+      <c r="L2" s="46" t="n"/>
+      <c r="M2" s="74" t="n"/>
+      <c r="N2" s="75" t="n"/>
+      <c r="O2" s="46" t="n"/>
+      <c r="P2" s="74" t="n"/>
+      <c r="Q2" s="75" t="n"/>
+      <c r="R2" s="46" t="n"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" s="4">
+      <c r="A3" s="70" t="n"/>
+      <c r="B3" s="72" t="n"/>
+      <c r="D3" s="70" t="n"/>
+      <c r="E3" s="72" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="70" t="n"/>
+      <c r="H3" s="72" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="70" t="n"/>
+      <c r="K3" s="72" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="70" t="n"/>
+      <c r="N3" s="72" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="70" t="n"/>
+      <c r="Q3" s="72" t="n"/>
+      <c r="R3" s="46" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" s="4"/>
+    <row r="5" ht="22.5" customHeight="1" s="4">
+      <c r="A5" s="1">
+        <f>IF('座席表 （低学年用）'!Y8="","",IFERROR(VLOOKUP('座席表 （低学年用）'!Y8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B5" s="69" t="n"/>
+      <c r="D5" s="1">
+        <f>IF('座席表 （低学年用）'!X8="","",IFERROR(VLOOKUP('座席表 （低学年用）'!X8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E5" s="69" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="1">
+        <f>IF('座席表 （低学年用）'!W8="","",IFERROR(VLOOKUP('座席表 （低学年用）'!W8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H5" s="69" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="1">
+        <f>IF('座席表 （低学年用）'!V8="","",IFERROR(VLOOKUP('座席表 （低学年用）'!V8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K5" s="69" t="n"/>
+      <c r="L5" s="46" t="n"/>
+      <c r="M5" s="1">
+        <f>IF('座席表 （低学年用）'!U8="","",IFERROR(VLOOKUP('座席表 （低学年用）'!U8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N5" s="69" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="1">
+        <f>IF('座席表 （低学年用）'!T8="","",IFERROR(VLOOKUP('座席表 （低学年用）'!T8,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="69" t="n"/>
+      <c r="R5" s="46" t="n"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" s="4">
+      <c r="A6" s="74" t="n"/>
+      <c r="B6" s="75" t="n"/>
+      <c r="D6" s="74" t="n"/>
+      <c r="E6" s="75" t="n"/>
+      <c r="F6" s="46" t="n"/>
+      <c r="G6" s="74" t="n"/>
+      <c r="H6" s="75" t="n"/>
+      <c r="I6" s="46" t="n"/>
+      <c r="J6" s="74" t="n"/>
+      <c r="K6" s="75" t="n"/>
+      <c r="L6" s="46" t="n"/>
+      <c r="M6" s="74" t="n"/>
+      <c r="N6" s="75" t="n"/>
+      <c r="O6" s="46" t="n"/>
+      <c r="P6" s="74" t="n"/>
+      <c r="Q6" s="75" t="n"/>
+      <c r="R6" s="46" t="n"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1" s="4">
+      <c r="A7" s="70" t="n"/>
+      <c r="B7" s="72" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="72" t="n"/>
+      <c r="F7" s="46" t="n"/>
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="72" t="n"/>
+      <c r="I7" s="46" t="n"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="72" t="n"/>
+      <c r="L7" s="46" t="n"/>
+      <c r="M7" s="70" t="n"/>
+      <c r="N7" s="72" t="n"/>
+      <c r="O7" s="46" t="n"/>
+      <c r="P7" s="70" t="n"/>
+      <c r="Q7" s="72" t="n"/>
+      <c r="R7" s="46" t="n"/>
+    </row>
+    <row r="8" ht="22.5" customHeight="1" s="4">
+      <c r="A8" s="45" t="n"/>
+      <c r="B8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="45" t="n"/>
+      <c r="G8" s="45" t="n"/>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="45" t="n"/>
+      <c r="J8" s="45" t="n"/>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="n"/>
+      <c r="M8" s="45" t="n"/>
+      <c r="N8" s="45" t="n"/>
+      <c r="O8" s="45" t="n"/>
+      <c r="P8" s="45" t="n"/>
+      <c r="Q8" s="45" t="n"/>
+      <c r="R8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="22.5" customHeight="1" s="4">
+      <c r="A9" s="1">
+        <f>IF('座席表 （低学年用）'!Y7="","",IFERROR(VLOOKUP('座席表 （低学年用）'!Y7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B9" s="69" t="n"/>
+      <c r="D9" s="1">
+        <f>IF('座席表 （低学年用）'!X7="","",IFERROR(VLOOKUP('座席表 （低学年用）'!X7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="69" t="n"/>
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="1">
+        <f>IF('座席表 （低学年用）'!W7="","",IFERROR(VLOOKUP('座席表 （低学年用）'!W7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H9" s="69" t="n"/>
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="1">
+        <f>IF('座席表 （低学年用）'!V7="","",IFERROR(VLOOKUP('座席表 （低学年用）'!V7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K9" s="69" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="1">
+        <f>IF('座席表 （低学年用）'!U7="","",IFERROR(VLOOKUP('座席表 （低学年用）'!U7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N9" s="69" t="n"/>
+      <c r="O9" s="46" t="n"/>
+      <c r="P9" s="1">
+        <f>IF('座席表 （低学年用）'!T7="","",IFERROR(VLOOKUP('座席表 （低学年用）'!T7,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="69" t="n"/>
+      <c r="R9" s="46" t="n"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" s="4">
+      <c r="A10" s="74" t="n"/>
+      <c r="B10" s="75" t="n"/>
+      <c r="D10" s="74" t="n"/>
+      <c r="E10" s="75" t="n"/>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="74" t="n"/>
+      <c r="H10" s="75" t="n"/>
+      <c r="I10" s="46" t="n"/>
+      <c r="J10" s="74" t="n"/>
+      <c r="K10" s="75" t="n"/>
+      <c r="L10" s="46" t="n"/>
+      <c r="M10" s="74" t="n"/>
+      <c r="N10" s="75" t="n"/>
+      <c r="O10" s="46" t="n"/>
+      <c r="P10" s="74" t="n"/>
+      <c r="Q10" s="75" t="n"/>
+      <c r="R10" s="46" t="n"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" s="4">
+      <c r="A11" s="70" t="n"/>
+      <c r="B11" s="72" t="n"/>
+      <c r="D11" s="70" t="n"/>
+      <c r="E11" s="72" t="n"/>
+      <c r="F11" s="46" t="n"/>
+      <c r="G11" s="70" t="n"/>
+      <c r="H11" s="72" t="n"/>
+      <c r="I11" s="46" t="n"/>
+      <c r="J11" s="70" t="n"/>
+      <c r="K11" s="72" t="n"/>
+      <c r="L11" s="46" t="n"/>
+      <c r="M11" s="70" t="n"/>
+      <c r="N11" s="72" t="n"/>
+      <c r="O11" s="46" t="n"/>
+      <c r="P11" s="70" t="n"/>
+      <c r="Q11" s="72" t="n"/>
+      <c r="R11" s="46" t="n"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" s="4">
+      <c r="A12" s="45" t="n"/>
+      <c r="B12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="45" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="45" t="n"/>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="45" t="n"/>
+      <c r="M12" s="45" t="n"/>
+      <c r="N12" s="45" t="n"/>
+      <c r="O12" s="45" t="n"/>
+      <c r="P12" s="45" t="n"/>
+      <c r="Q12" s="45" t="n"/>
+      <c r="R12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1" s="4">
+      <c r="A13" s="1">
+        <f>IF('座席表 （低学年用）'!Y6="","",IFERROR(VLOOKUP('座席表 （低学年用）'!Y6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B13" s="69" t="n"/>
+      <c r="D13" s="1">
+        <f>IF('座席表 （低学年用）'!X6="","",IFERROR(VLOOKUP('座席表 （低学年用）'!X6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="69" t="n"/>
+      <c r="F13" s="46" t="n"/>
+      <c r="G13" s="1">
+        <f>IF('座席表 （低学年用）'!W6="","",IFERROR(VLOOKUP('座席表 （低学年用）'!W6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H13" s="69" t="n"/>
+      <c r="I13" s="46" t="n"/>
+      <c r="J13" s="1">
+        <f>IF('座席表 （低学年用）'!V6="","",IFERROR(VLOOKUP('座席表 （低学年用）'!V6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K13" s="69" t="n"/>
+      <c r="L13" s="46" t="n"/>
+      <c r="M13" s="1">
+        <f>IF('座席表 （低学年用）'!U6="","",IFERROR(VLOOKUP('座席表 （低学年用）'!U6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N13" s="69" t="n"/>
+      <c r="O13" s="46" t="n"/>
+      <c r="P13" s="1">
+        <f>IF('座席表 （低学年用）'!T6="","",IFERROR(VLOOKUP('座席表 （低学年用）'!T6,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="69" t="n"/>
+      <c r="R13" s="46" t="n"/>
+    </row>
+    <row r="14" ht="22.5" customHeight="1" s="4">
+      <c r="A14" s="74" t="n"/>
+      <c r="B14" s="75" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="75" t="n"/>
+      <c r="F14" s="46" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="75" t="n"/>
+      <c r="I14" s="46" t="n"/>
+      <c r="J14" s="74" t="n"/>
+      <c r="K14" s="75" t="n"/>
+      <c r="L14" s="46" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="75" t="n"/>
+      <c r="O14" s="46" t="n"/>
+      <c r="P14" s="74" t="n"/>
+      <c r="Q14" s="75" t="n"/>
+      <c r="R14" s="46" t="n"/>
+    </row>
+    <row r="15" ht="22.5" customHeight="1" s="4">
+      <c r="A15" s="70" t="n"/>
+      <c r="B15" s="72" t="n"/>
+      <c r="D15" s="70" t="n"/>
+      <c r="E15" s="72" t="n"/>
+      <c r="F15" s="46" t="n"/>
+      <c r="G15" s="70" t="n"/>
+      <c r="H15" s="72" t="n"/>
+      <c r="I15" s="46" t="n"/>
+      <c r="J15" s="70" t="n"/>
+      <c r="K15" s="72" t="n"/>
+      <c r="L15" s="46" t="n"/>
+      <c r="M15" s="70" t="n"/>
+      <c r="N15" s="72" t="n"/>
+      <c r="O15" s="46" t="n"/>
+      <c r="P15" s="70" t="n"/>
+      <c r="Q15" s="72" t="n"/>
+      <c r="R15" s="46" t="n"/>
+    </row>
+    <row r="16" ht="22.5" customHeight="1" s="4">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="45" t="n"/>
+      <c r="G16" s="45" t="n"/>
+      <c r="H16" s="45" t="n"/>
+      <c r="I16" s="45" t="n"/>
+      <c r="J16" s="45" t="n"/>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="45" t="n"/>
+      <c r="M16" s="45" t="n"/>
+      <c r="N16" s="45" t="n"/>
+      <c r="O16" s="45" t="n"/>
+      <c r="P16" s="45" t="n"/>
+      <c r="Q16" s="45" t="n"/>
+      <c r="R16" s="45" t="n"/>
+    </row>
+    <row r="17" ht="22.5" customHeight="1" s="4">
+      <c r="A17" s="1">
+        <f>IF('座席表 （低学年用）'!Y5="","",IFERROR(VLOOKUP('座席表 （低学年用）'!Y5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B17" s="69" t="n"/>
+      <c r="D17" s="1">
+        <f>IF('座席表 （低学年用）'!X5="","",IFERROR(VLOOKUP('座席表 （低学年用）'!X5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="69" t="n"/>
+      <c r="F17" s="46" t="n"/>
+      <c r="G17" s="1">
+        <f>IF('座席表 （低学年用）'!W5="","",IFERROR(VLOOKUP('座席表 （低学年用）'!W5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H17" s="69" t="n"/>
+      <c r="I17" s="46" t="n"/>
+      <c r="J17" s="1">
+        <f>IF('座席表 （低学年用）'!V5="","",IFERROR(VLOOKUP('座席表 （低学年用）'!V5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K17" s="69" t="n"/>
+      <c r="L17" s="46" t="n"/>
+      <c r="M17" s="1">
+        <f>IF('座席表 （低学年用）'!U5="","",IFERROR(VLOOKUP('座席表 （低学年用）'!U5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N17" s="69" t="n"/>
+      <c r="O17" s="46" t="n"/>
+      <c r="P17" s="1">
+        <f>IF('座席表 （低学年用）'!T5="","",IFERROR(VLOOKUP('座席表 （低学年用）'!T5,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="69" t="n"/>
+      <c r="R17" s="46" t="n"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1" s="4">
+      <c r="A18" s="74" t="n"/>
+      <c r="B18" s="75" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="75" t="n"/>
+      <c r="F18" s="46" t="n"/>
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="75" t="n"/>
+      <c r="I18" s="46" t="n"/>
+      <c r="J18" s="74" t="n"/>
+      <c r="K18" s="75" t="n"/>
+      <c r="L18" s="46" t="n"/>
+      <c r="M18" s="74" t="n"/>
+      <c r="N18" s="75" t="n"/>
+      <c r="O18" s="46" t="n"/>
+      <c r="P18" s="74" t="n"/>
+      <c r="Q18" s="75" t="n"/>
+      <c r="R18" s="46" t="n"/>
+    </row>
+    <row r="19" ht="22.5" customHeight="1" s="4">
+      <c r="A19" s="70" t="n"/>
+      <c r="B19" s="72" t="n"/>
+      <c r="D19" s="70" t="n"/>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="46" t="n"/>
+      <c r="G19" s="70" t="n"/>
+      <c r="H19" s="72" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="70" t="n"/>
+      <c r="K19" s="72" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="70" t="n"/>
+      <c r="N19" s="72" t="n"/>
+      <c r="O19" s="46" t="n"/>
+      <c r="P19" s="70" t="n"/>
+      <c r="Q19" s="72" t="n"/>
+      <c r="R19" s="46" t="n"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1" s="4">
+      <c r="A20" s="45" t="n"/>
+      <c r="B20" s="45" t="n"/>
+      <c r="D20" s="45" t="n"/>
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="45" t="n"/>
+      <c r="G20" s="45" t="n"/>
+      <c r="H20" s="45" t="n"/>
+      <c r="I20" s="45" t="n"/>
+      <c r="J20" s="45" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="45" t="n"/>
+      <c r="N20" s="45" t="n"/>
+      <c r="O20" s="45" t="n"/>
+      <c r="P20" s="45" t="n"/>
+      <c r="Q20" s="45" t="n"/>
+      <c r="R20" s="45" t="n"/>
+    </row>
+    <row r="21" ht="22.5" customHeight="1" s="4">
+      <c r="A21" s="1">
+        <f>IF('座席表 （低学年用）'!Y4="","",IFERROR(VLOOKUP('座席表 （低学年用）'!Y4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="B21" s="69" t="n"/>
+      <c r="D21" s="1">
+        <f>IF('座席表 （低学年用）'!X4="","",IFERROR(VLOOKUP('座席表 （低学年用）'!X4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="69" t="n"/>
+      <c r="F21" s="46" t="n"/>
+      <c r="G21" s="1">
+        <f>IF('座席表 （低学年用）'!W4="","",IFERROR(VLOOKUP('座席表 （低学年用）'!W4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="H21" s="69" t="n"/>
+      <c r="I21" s="46" t="n"/>
+      <c r="J21" s="1">
+        <f>IF('座席表 （低学年用）'!V4="","",IFERROR(VLOOKUP('座席表 （低学年用）'!V4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="K21" s="69" t="n"/>
+      <c r="L21" s="46" t="n"/>
+      <c r="M21" s="1">
+        <f>IF('座席表 （低学年用）'!U4="","",IFERROR(VLOOKUP('座席表 （低学年用）'!U4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="N21" s="69" t="n"/>
+      <c r="O21" s="46" t="n"/>
+      <c r="P21" s="1">
+        <f>IF('座席表 （低学年用）'!T4="","",IFERROR(VLOOKUP('座席表 （低学年用）'!T4,名簿!$B$3:$D$37,3,FALSE()),""))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="69" t="n"/>
+      <c r="R21" s="45" t="n"/>
+    </row>
+    <row r="22" ht="22.5" customHeight="1" s="4">
+      <c r="A22" s="74" t="n"/>
+      <c r="B22" s="75" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="75" t="n"/>
+      <c r="F22" s="46" t="n"/>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="75" t="n"/>
+      <c r="I22" s="46" t="n"/>
+      <c r="J22" s="74" t="n"/>
+      <c r="K22" s="75" t="n"/>
+      <c r="L22" s="46" t="n"/>
+      <c r="M22" s="74" t="n"/>
+      <c r="N22" s="75" t="n"/>
+      <c r="O22" s="46" t="n"/>
+      <c r="P22" s="74" t="n"/>
+      <c r="Q22" s="75" t="n"/>
+      <c r="R22" s="45" t="n"/>
+    </row>
+    <row r="23" ht="22.5" customHeight="1" s="4">
+      <c r="A23" s="70" t="n"/>
+      <c r="B23" s="72" t="n"/>
+      <c r="D23" s="70" t="n"/>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="46" t="n"/>
+      <c r="G23" s="70" t="n"/>
+      <c r="H23" s="72" t="n"/>
+      <c r="I23" s="46" t="n"/>
+      <c r="J23" s="70" t="n"/>
+      <c r="K23" s="72" t="n"/>
+      <c r="L23" s="46" t="n"/>
+      <c r="M23" s="70" t="n"/>
+      <c r="N23" s="72" t="n"/>
+      <c r="O23" s="46" t="n"/>
+      <c r="P23" s="70" t="n"/>
+      <c r="Q23" s="72" t="n"/>
+      <c r="R23" s="45" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1" s="4"/>
+    <row r="25" ht="13.5" customHeight="1" s="4">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>黒板</t>
+        </is>
+      </c>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="68" t="n"/>
+      <c r="J25" s="68" t="n"/>
+      <c r="K25" s="69" t="n"/>
+    </row>
+    <row r="26" ht="22.5" customHeight="1" s="4">
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="71" t="n"/>
+      <c r="I26" s="71" t="n"/>
+      <c r="J26" s="71" t="n"/>
+      <c r="K26" s="72" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="J5:K7"/>
+    <mergeCell ref="P5:Q7"/>
+    <mergeCell ref="A9:B11"/>
+    <mergeCell ref="P1:Q3"/>
+    <mergeCell ref="J17:K19"/>
+    <mergeCell ref="J1:K3"/>
+    <mergeCell ref="M9:N11"/>
+    <mergeCell ref="M5:N7"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="J13:K15"/>
+    <mergeCell ref="G21:H23"/>
+    <mergeCell ref="G17:H19"/>
+    <mergeCell ref="D21:E23"/>
+    <mergeCell ref="G13:H15"/>
+    <mergeCell ref="G25:K26"/>
+    <mergeCell ref="D17:E19"/>
+    <mergeCell ref="J9:K11"/>
+    <mergeCell ref="P9:Q11"/>
+    <mergeCell ref="M1:N3"/>
+    <mergeCell ref="P21:Q23"/>
+    <mergeCell ref="D13:E15"/>
+    <mergeCell ref="P13:Q15"/>
+    <mergeCell ref="M13:N15"/>
+    <mergeCell ref="G1:H3"/>
+    <mergeCell ref="A21:B23"/>
+    <mergeCell ref="P17:Q19"/>
+    <mergeCell ref="A17:B19"/>
+    <mergeCell ref="M21:N23"/>
+    <mergeCell ref="D5:E7"/>
+    <mergeCell ref="G5:H7"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="D9:E11"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="J21:K23"/>
+    <mergeCell ref="D1:E3"/>
+    <mergeCell ref="G9:H11"/>
+    <mergeCell ref="A13:B15"/>
+  </mergeCells>
+  <pageMargins left="0.197916666666667" right="0.125" top="0.291666666666667" bottom="0.21875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7365,7 +8627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7405,7 +8667,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" s="4">
+    <row r="3" ht="21" customHeight="1" s="4">
       <c r="A3" s="85" t="inlineStr">
         <is>
           <t>番号</t>
@@ -7442,7 +8704,7 @@
       </c>
       <c r="P3" s="87" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" s="4">
+    <row r="4" ht="21" customHeight="1" s="4">
       <c r="A4" s="79">
         <f>名簿!B3</f>
         <v/>
@@ -7489,7 +8751,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="4">
+    <row r="5" ht="21" customHeight="1" s="4">
       <c r="A5" s="79">
         <f>名簿!B4</f>
         <v/>
@@ -7536,7 +8798,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" s="4">
+    <row r="6" ht="21" customHeight="1" s="4">
       <c r="A6" s="79">
         <f>名簿!B5</f>
         <v/>
@@ -7583,7 +8845,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" s="4">
+    <row r="7" ht="21" customHeight="1" s="4">
       <c r="A7" s="79">
         <f>名簿!B6</f>
         <v/>
@@ -7630,7 +8892,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" s="4">
+    <row r="8" ht="21" customHeight="1" s="4">
       <c r="A8" s="81">
         <f>名簿!B7</f>
         <v/>
@@ -7677,7 +8939,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" s="4">
+    <row r="9" ht="21" customHeight="1" s="4">
       <c r="A9" s="79">
         <f>名簿!B8</f>
         <v/>
@@ -7724,7 +8986,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" s="4">
+    <row r="10" ht="21" customHeight="1" s="4">
       <c r="A10" s="79">
         <f>名簿!B9</f>
         <v/>
@@ -7771,7 +9033,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" s="4">
+    <row r="11" ht="21" customHeight="1" s="4">
       <c r="A11" s="79">
         <f>名簿!B10</f>
         <v/>
@@ -7818,7 +9080,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="4">
+    <row r="12" ht="21" customHeight="1" s="4">
       <c r="A12" s="79">
         <f>名簿!B11</f>
         <v/>
@@ -7833,7 +9095,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" s="4">
+    <row r="13" ht="21" customHeight="1" s="4">
       <c r="A13" s="81">
         <f>名簿!B12</f>
         <v/>
@@ -7868,7 +9130,7 @@
       </c>
       <c r="P13" s="87" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1" s="4">
+    <row r="14" ht="21" customHeight="1" s="4">
       <c r="A14" s="79">
         <f>名簿!B13</f>
         <v/>
@@ -7915,7 +9177,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="4">
+    <row r="15" ht="21" customHeight="1" s="4">
       <c r="A15" s="79">
         <f>名簿!B14</f>
         <v/>
@@ -7962,7 +9224,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="4">
+    <row r="16" ht="21" customHeight="1" s="4">
       <c r="A16" s="79">
         <f>名簿!B15</f>
         <v/>
@@ -8009,7 +9271,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" s="4">
+    <row r="17" ht="21" customHeight="1" s="4">
       <c r="A17" s="79">
         <f>名簿!B16</f>
         <v/>
@@ -8056,7 +9318,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" s="4">
+    <row r="18" ht="21" customHeight="1" s="4">
       <c r="A18" s="81">
         <f>名簿!B17</f>
         <v/>
@@ -8103,7 +9365,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" s="4">
+    <row r="19" ht="21" customHeight="1" s="4">
       <c r="A19" s="79">
         <f>名簿!B18</f>
         <v/>
@@ -8150,7 +9412,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" s="4">
+    <row r="20" ht="21" customHeight="1" s="4">
       <c r="A20" s="79">
         <f>名簿!B19</f>
         <v/>
@@ -8197,7 +9459,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" s="4">
+    <row r="21" ht="21" customHeight="1" s="4">
       <c r="A21" s="79">
         <f>名簿!B20</f>
         <v/>
@@ -8244,7 +9506,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="4">
+    <row r="22" ht="21" customHeight="1" s="4">
       <c r="A22" s="79">
         <f>名簿!B21</f>
         <v/>
@@ -8259,7 +9521,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="4">
+    <row r="23" ht="21" customHeight="1" s="4">
       <c r="A23" s="81">
         <f>名簿!B22</f>
         <v/>
@@ -8274,7 +9536,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="4">
+    <row r="24" ht="21" customHeight="1" s="4">
       <c r="A24" s="79">
         <f>名簿!B23</f>
         <v/>
@@ -8289,7 +9551,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="4">
+    <row r="25" ht="21" customHeight="1" s="4">
       <c r="A25" s="79">
         <f>名簿!B24</f>
         <v/>
@@ -8304,7 +9566,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="4">
+    <row r="26" ht="21" customHeight="1" s="4">
       <c r="A26" s="79">
         <f>名簿!B25</f>
         <v/>
@@ -8319,7 +9581,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="4">
+    <row r="27" ht="21" customHeight="1" s="4">
       <c r="A27" s="79">
         <f>名簿!B26</f>
         <v/>
@@ -8334,7 +9596,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="4">
+    <row r="28" ht="21" customHeight="1" s="4">
       <c r="A28" s="81">
         <f>名簿!B27</f>
         <v/>
@@ -8349,7 +9611,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="4">
+    <row r="29" ht="21" customHeight="1" s="4">
       <c r="A29" s="79">
         <f>名簿!B28</f>
         <v/>
@@ -8364,7 +9626,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="4">
+    <row r="30" ht="21" customHeight="1" s="4">
       <c r="A30" s="79">
         <f>名簿!B29</f>
         <v/>
@@ -8379,7 +9641,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="4">
+    <row r="31" ht="21" customHeight="1" s="4">
       <c r="A31" s="79">
         <f>名簿!B30</f>
         <v/>
@@ -8394,7 +9656,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="4">
+    <row r="32" ht="21" customHeight="1" s="4">
       <c r="A32" s="79">
         <f>名簿!B31</f>
         <v/>
@@ -8409,7 +9671,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="4">
+    <row r="33" ht="21" customHeight="1" s="4">
       <c r="A33" s="81">
         <f>名簿!B32</f>
         <v/>
@@ -8424,7 +9686,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="4">
+    <row r="34" ht="21" customHeight="1" s="4">
       <c r="A34" s="79">
         <f>名簿!B33</f>
         <v/>
@@ -8439,7 +9701,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="4">
+    <row r="35" ht="21" customHeight="1" s="4">
       <c r="A35" s="79">
         <f>名簿!B34</f>
         <v/>
@@ -8454,7 +9716,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="4">
+    <row r="36" ht="21" customHeight="1" s="4">
       <c r="A36" s="79">
         <f>名簿!B35</f>
         <v/>
@@ -8469,7 +9731,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="4">
+    <row r="37" ht="21" customHeight="1" s="4">
       <c r="A37" s="79">
         <f>名簿!B36</f>
         <v/>
@@ -8484,7 +9746,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="4">
+    <row r="38" ht="21" customHeight="1" s="4">
       <c r="A38" s="81">
         <f>名簿!B37</f>
         <v/>
@@ -8534,215 +9796,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" style="4" min="1" max="1"/>
-    <col width="30" customWidth="1" style="4" min="2" max="2"/>
-    <col width="66" customWidth="1" style="4" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="4">
-      <c r="B1" s="97" t="inlineStr">
-        <is>
-          <t>使い方</t>
-        </is>
-      </c>
-      <c r="C1" s="98" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="4">
-      <c r="B2" s="98" t="n"/>
-      <c r="C2" s="98" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1" s="4">
-      <c r="B3" s="98" t="inlineStr">
-        <is>
-          <t>① 名簿を入力</t>
-        </is>
-      </c>
-      <c r="C3" s="98" t="inlineStr">
-        <is>
-          <t>「名簿」シートに、漢字氏名とかな氏名を入力します。ほかのシートには自動で名前が入ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="4">
-      <c r="B4" s="98" t="inlineStr">
-        <is>
-          <t>② 漢字かひらがなを選ぶ</t>
-        </is>
-      </c>
-      <c r="C4" s="98" t="inlineStr">
-        <is>
-          <t>「名簿」シートの「名前の表示」で「漢字」か「ひらがな」を選びます（低学年はひらがな）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" s="4">
-      <c r="B5" s="98" t="inlineStr">
-        <is>
-          <t>③ 印刷したいシートを開く</t>
-        </is>
-      </c>
-      <c r="C5" s="98" t="inlineStr">
-        <is>
-          <t>下の表から選んで、拡大・縮小なし（100%）で印刷します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="4">
-      <c r="B6" s="98" t="n"/>
-      <c r="C6" s="98" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="4">
-      <c r="B7" s="99" t="inlineStr">
-        <is>
-          <t>シート名</t>
-        </is>
-      </c>
-      <c r="C7" s="99" t="inlineStr">
-        <is>
-          <t>用途・用紙</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="4">
-      <c r="B8" s="100" t="inlineStr">
-        <is>
-          <t>名前カード</t>
-        </is>
-      </c>
-      <c r="C8" s="100" t="inlineStr">
-        <is>
-          <t>A3縦・36人。ふりがな付き</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="4">
-      <c r="B9" s="100" t="inlineStr">
-        <is>
-          <t>名前カード (大) / (小)</t>
-        </is>
-      </c>
-      <c r="C9" s="100" t="inlineStr">
-        <is>
-          <t>A3縦・10人 / 40人。ふりがな付き</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="4">
-      <c r="B10" s="100" t="inlineStr">
-        <is>
-          <t>縦書き (大) / (中) / (小)</t>
-        </is>
-      </c>
-      <c r="C10" s="100" t="inlineStr">
-        <is>
-          <t>A3横・10人 / 20人 / 36人。ふりがなは名前の右側</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="4">
-      <c r="B11" s="100" t="inlineStr">
-        <is>
-          <t>〇〇 (ふりがななし)</t>
-        </is>
-      </c>
-      <c r="C11" s="100" t="inlineStr">
-        <is>
-          <t>上と同じ大きさで、ふりがなを付けないカード。名前がカードの真ん中にきます。ひらがな表示のときはこちらを使います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="4">
-      <c r="B12" s="100" t="inlineStr">
-        <is>
-          <t>座席表 / 座席表 （低学年用）</t>
-        </is>
-      </c>
-      <c r="C12" s="100" t="inlineStr">
-        <is>
-          <t>黄色の欄に出席番号を入力すると座席表ができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="4">
-      <c r="B13" s="100" t="inlineStr">
-        <is>
-          <t>提出物チェック表</t>
-        </is>
-      </c>
-      <c r="C13" s="100" t="inlineStr">
-        <is>
-          <t>黄色の欄に題名と提出物名を入力。未提出の数を自動で数えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="4">
-      <c r="B14" s="100" t="inlineStr">
-        <is>
-          <t>班分け表</t>
-        </is>
-      </c>
-      <c r="C14" s="100" t="inlineStr">
-        <is>
-          <t>黄色の欄に班の番号（1〜8）を入力すると、班ごとの名簿ができます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="4">
-      <c r="B15" s="98" t="n"/>
-      <c r="C15" s="98" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" s="4">
-      <c r="B16" s="101" t="inlineStr">
-        <is>
-          <t>メモ</t>
-        </is>
-      </c>
-      <c r="C16" s="98" t="inlineStr">
-        <is>
-          <t>黄色のセルが入力するところです。それ以外のセルには数式が入っているので、消さないようにしてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1" s="4">
-      <c r="B17" s="98" t="n"/>
-      <c r="C17" s="98" t="inlineStr">
-        <is>
-          <t>カードの大きさの一覧は「名簿」シートの右側にあります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1" s="4">
-      <c r="B18" s="98" t="n"/>
-      <c r="C18" s="98" t="inlineStr">
-        <is>
-          <t>名前の長い人は、カードの枠に入るように文字が自動で小さくなります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1" s="4">
-      <c r="B19" s="98" t="n"/>
-      <c r="C19" s="98" t="inlineStr">
-        <is>
-          <t>名前が入っていないカードは枠も印刷されません（元からある「名前カード」を除く）。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.236" right="0.236" top="0.236" bottom="0.236" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9088,6 +10141,227 @@
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.270833333333333" bottom="0.40625" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" style="4" min="1" max="1"/>
+    <col width="30" customWidth="1" style="4" min="2" max="2"/>
+    <col width="66" customWidth="1" style="4" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="4">
+      <c r="B1" s="97" t="inlineStr">
+        <is>
+          <t>使い方</t>
+        </is>
+      </c>
+      <c r="C1" s="98" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="4">
+      <c r="B2" s="98" t="n"/>
+      <c r="C2" s="98" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="4">
+      <c r="B3" s="98" t="inlineStr">
+        <is>
+          <t>① 名簿を入力</t>
+        </is>
+      </c>
+      <c r="C3" s="98" t="inlineStr">
+        <is>
+          <t>「名簿」シートに、漢字氏名とかな氏名を入力します。ほかのシートには自動で名前が入ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="4">
+      <c r="B4" s="98" t="inlineStr">
+        <is>
+          <t>② 漢字かひらがなを選ぶ</t>
+        </is>
+      </c>
+      <c r="C4" s="98" t="inlineStr">
+        <is>
+          <t>「名簿」シートの「名前の表示」で「漢字」か「ひらがな」を選びます（低学年はひらがな）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="4">
+      <c r="B5" s="98" t="inlineStr">
+        <is>
+          <t>③ 印刷したいシートを開く</t>
+        </is>
+      </c>
+      <c r="C5" s="98" t="inlineStr">
+        <is>
+          <t>下の表から選んで、拡大・縮小なし（100%）で印刷します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="4">
+      <c r="B6" s="98" t="n"/>
+      <c r="C6" s="98" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="4">
+      <c r="B7" s="99" t="inlineStr">
+        <is>
+          <t>シート名</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="inlineStr">
+        <is>
+          <t>用途・用紙</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="4">
+      <c r="B8" s="100" t="inlineStr">
+        <is>
+          <t>名前カード</t>
+        </is>
+      </c>
+      <c r="C8" s="100" t="inlineStr">
+        <is>
+          <t>A3縦・36人。ふりがな付き</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="4">
+      <c r="B9" s="100" t="inlineStr">
+        <is>
+          <t>名前カード (大) / (小)</t>
+        </is>
+      </c>
+      <c r="C9" s="100" t="inlineStr">
+        <is>
+          <t>A3縦・10人 / 40人。ふりがな付き</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="4">
+      <c r="B10" s="100" t="inlineStr">
+        <is>
+          <t>縦書き (大) / (中) / (小)</t>
+        </is>
+      </c>
+      <c r="C10" s="100" t="inlineStr">
+        <is>
+          <t>A3横・10人 / 20人 / 36人。ふりがなは名前の右側</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="4">
+      <c r="B11" s="100" t="inlineStr">
+        <is>
+          <t>〇〇 (ふりがななし)</t>
+        </is>
+      </c>
+      <c r="C11" s="100" t="inlineStr">
+        <is>
+          <t>上と同じ大きさで、ふりがなを付けないカード。名前がカードの真ん中にきます。ひらがな表示のときはこちらを使います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="4">
+      <c r="B12" s="100" t="inlineStr">
+        <is>
+          <t>座席表 / 座席表 （低学年用）</t>
+        </is>
+      </c>
+      <c r="C12" s="100" t="inlineStr">
+        <is>
+          <t>黄色の欄に出席番号を入力すると座席表ができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="4">
+      <c r="B13" s="100" t="inlineStr">
+        <is>
+          <t>座席表 (黒板が下) / （低学年用・黒板が下）</t>
+        </is>
+      </c>
+      <c r="C13" s="100" t="inlineStr">
+        <is>
+          <t>黒板を背にした先生から見た向きの座席表。元の座席表に入力した席順が自動で出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="4">
+      <c r="B14" s="100" t="inlineStr">
+        <is>
+          <t>提出物チェック表</t>
+        </is>
+      </c>
+      <c r="C14" s="100" t="inlineStr">
+        <is>
+          <t>黄色の欄に題名と提出物名を入力。未提出の数を自動で数えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="4">
+      <c r="B15" s="100" t="inlineStr">
+        <is>
+          <t>班分け表</t>
+        </is>
+      </c>
+      <c r="C15" s="100" t="inlineStr">
+        <is>
+          <t>黄色の欄に班の番号（1〜8）を入力すると、班ごとの名簿ができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="4">
+      <c r="B16" s="98" t="n"/>
+      <c r="C16" s="98" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="4">
+      <c r="B17" s="101" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+      <c r="C17" s="98" t="inlineStr">
+        <is>
+          <t>黄色のセルが入力するところです。それ以外のセルには数式が入っているので、消さないようにしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="4">
+      <c r="B18" s="98" t="n"/>
+      <c r="C18" s="98" t="inlineStr">
+        <is>
+          <t>カードの大きさの一覧は「名簿」シートの右側にあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="4">
+      <c r="B19" s="98" t="n"/>
+      <c r="C19" s="98" t="inlineStr">
+        <is>
+          <t>名前の長い人は、カードの枠に入るように文字が自動で小さくなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="4">
+      <c r="B20" s="98" t="n"/>
+      <c r="C20" s="98" t="inlineStr">
+        <is>
+          <t>名前が入っていないカードは枠も印刷されません（元からある「名前カード」を除く）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.236" right="0.236" top="0.236" bottom="0.236" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
